--- a/Experiment3/Workspace/Models/data/25/response_distribution.xlsx
+++ b/Experiment3/Workspace/Models/data/25/response_distribution.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,13 +477,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D2" t="n">
-        <v>8.426666666666666</v>
+        <v>8.379710144927536</v>
       </c>
       <c r="E2" t="n">
-        <v>1.449398690598265</v>
+        <v>1.469830091001549</v>
       </c>
       <c r="F2" t="n">
         <v>2</v>
@@ -504,13 +504,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D3" t="n">
-        <v>7.482666666666667</v>
+        <v>7.355072463768116</v>
       </c>
       <c r="E3" t="n">
-        <v>2.104504250350157</v>
+        <v>2.123203499594901</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -531,13 +531,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D4" t="n">
-        <v>7.448</v>
+        <v>7.318840579710145</v>
       </c>
       <c r="E4" t="n">
-        <v>2.137925076214945</v>
+        <v>2.157060527589842</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -558,13 +558,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D5" t="n">
-        <v>7.261333333333333</v>
+        <v>7.121739130434783</v>
       </c>
       <c r="E5" t="n">
-        <v>2.218618469402206</v>
+        <v>2.231771479711535</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D6" t="n">
-        <v>1.612</v>
+        <v>1.660869565217391</v>
       </c>
       <c r="E6" t="n">
-        <v>0.97778529619097</v>
+        <v>0.9982884324096066</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D7" t="n">
-        <v>4.557333333333333</v>
+        <v>4.534782608695652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6826425785692366</v>
+        <v>0.6958984308878688</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
@@ -639,13 +639,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D8" t="n">
-        <v>2.550666666666667</v>
+        <v>2.440579710144927</v>
       </c>
       <c r="E8" t="n">
-        <v>1.450369257649099</v>
+        <v>1.396690972318739</v>
       </c>
       <c r="F8" t="n">
         <v>1</v>
@@ -666,13 +666,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D9" t="n">
-        <v>2.408</v>
+        <v>2.472463768115942</v>
       </c>
       <c r="E9" t="n">
-        <v>1.265307869785237</v>
+        <v>1.228576536933431</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
@@ -693,13 +693,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D10" t="n">
-        <v>2.56</v>
+        <v>2.473913043478261</v>
       </c>
       <c r="E10" t="n">
-        <v>1.363651737583764</v>
+        <v>1.30758112957655</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D11" t="n">
-        <v>6.682666666666667</v>
+        <v>6.555072463768116</v>
       </c>
       <c r="E11" t="n">
-        <v>2.118793352181351</v>
+        <v>2.150507837001654</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D12" t="n">
-        <v>6.173333333333333</v>
+        <v>6.26231884057971</v>
       </c>
       <c r="E12" t="n">
-        <v>1.39877242894124</v>
+        <v>1.392244895428336</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D13" t="n">
-        <v>7.553333333333334</v>
+        <v>7.423188405797101</v>
       </c>
       <c r="E13" t="n">
-        <v>1.811315371045787</v>
+        <v>1.80727002483886</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D14" t="n">
-        <v>5.945333333333333</v>
+        <v>5.934782608695652</v>
       </c>
       <c r="E14" t="n">
-        <v>1.773849000316389</v>
+        <v>1.755797040464053</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -828,13 +828,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D15" t="n">
-        <v>7.793333333333333</v>
+        <v>7.723188405797101</v>
       </c>
       <c r="E15" t="n">
-        <v>1.632843264081286</v>
+        <v>1.662411640004752</v>
       </c>
       <c r="F15" t="n">
         <v>2</v>
@@ -855,13 +855,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>750</v>
+        <v>690</v>
       </c>
       <c r="D16" t="n">
-        <v>4.504</v>
+        <v>4.51304347826087</v>
       </c>
       <c r="E16" t="n">
-        <v>1.729925100827383</v>
+        <v>1.788685049723804</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
